--- a/output/upload/S00027_1228_연금저축_하이드림연금보험.xlsx
+++ b/output/upload/S00027_1228_연금저축_하이드림연금보험.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW48"/>
+  <dimension ref="A1:AW198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -3061,11 +3061,11 @@
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>X55</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -3144,11 +3144,11 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X56</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -3227,11 +3227,11 @@
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>X57</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3306,11 +3306,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X58</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3351,11 +3351,11 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X59</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3396,11 +3396,11 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3441,11 +3441,11 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X61</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3486,11 +3486,11 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>999</v>
+        <v>61</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>X62</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3531,11 +3531,11 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X63</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3576,11 +3576,11 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>X64</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3666,11 +3666,11 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X66</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3711,11 +3711,11 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X67</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3756,11 +3756,11 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X68</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3801,11 +3801,11 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>999</v>
+        <v>68</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>X69</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3846,11 +3846,11 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3891,11 +3891,11 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>X71</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3936,11 +3936,11 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X72</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3981,11 +3981,11 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X73</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4026,11 +4026,11 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X74</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4071,11 +4071,11 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X75</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4116,11 +4116,11 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>999</v>
+        <v>75</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>X76</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4161,11 +4161,11 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X77</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4206,11 +4206,11 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>X78</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4251,11 +4251,11 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X79</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4296,11 +4296,11 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4341,11 +4341,11 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4431,11 +4431,11 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>999</v>
+        <v>7</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X55</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4656,11 +4656,11 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X56</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4701,11 +4701,11 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X57</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4746,11 +4746,11 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>999</v>
+        <v>57</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4778,26 +4778,6776 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>999</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>58</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>999</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>59</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>999</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>60</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>999</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>61</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>999</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>62</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>999</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>63</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>999</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>64</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>999</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>65</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>999</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>66</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>999</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>67</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>999</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>68</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>999</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>69</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>999</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>70</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>999</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>71</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>999</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>72</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>999</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>73</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>999</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>74</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>999</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>75</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>999</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>76</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>999</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>77</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>999</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>78</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>999</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>79</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>999</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>80</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>999</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>999</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>7</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>999</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>10</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>999</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>15</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>999</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>20</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
           <t>N0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>999</v>
-      </c>
-      <c r="M48" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>999</v>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N48" t="n">
+      <c r="N76" t="n">
         <v>0</v>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>999</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>55</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>999</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>56</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>999</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>57</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>999</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>58</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>999</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>59</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>999</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>60</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>999</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>61</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>999</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>62</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>999</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>63</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>999</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>64</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>999</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>65</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>999</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>66</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>999</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>67</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>999</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>68</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>999</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>69</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>999</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>70</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>999</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>71</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>999</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>72</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>999</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>73</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>999</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>74</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>999</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>75</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>999</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>76</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>999</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>77</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>999</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>78</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>999</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>79</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>999</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>80</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>999</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>5</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>999</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>7</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>999</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>10</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>999</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>15</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>999</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>20</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>999</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>999</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>55</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>999</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>56</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>999</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>57</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>999</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>58</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>999</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>59</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>999</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>60</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>999</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>61</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>999</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>62</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>999</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>63</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>999</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>64</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>999</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>65</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>999</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>66</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>999</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>67</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>999</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>68</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>999</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>69</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>999</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>70</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>999</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>71</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>999</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>72</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>999</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>73</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>999</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>74</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>999</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>75</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>999</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>76</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>999</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>77</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>999</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>78</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>999</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>79</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>999</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>80</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>999</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>5</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>999</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>7</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>999</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>10</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>999</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>15</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>999</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>20</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>999</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>999</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>55</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>999</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>56</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>999</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>57</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>999</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>58</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>999</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>59</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>999</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>60</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>999</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>61</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>999</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>62</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>999</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>63</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>999</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>64</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>999</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>65</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>999</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>66</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>999</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>67</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>999</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>68</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>999</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>69</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>999</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>70</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>999</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>71</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>999</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>72</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>999</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>73</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>999</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>74</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>999</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>75</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>999</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>76</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>999</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>77</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>999</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>78</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>999</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>79</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>999</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>80</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>999</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>5</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>999</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>7</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>999</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>10</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>999</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>15</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>999</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>20</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>999</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>999</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>55</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>999</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>56</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>999</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>57</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>999</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>58</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>999</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>59</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>999</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>60</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>999</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>61</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>999</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>62</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>999</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>63</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>999</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>64</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>999</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>65</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>999</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>66</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>999</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>67</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>999</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>68</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>999</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>69</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>999</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>70</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>999</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>71</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>999</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>72</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>999</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>73</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>999</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>74</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>999</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>75</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>999</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>76</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>999</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>77</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
+        <v>999</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>78</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>999</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>79</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>999</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>80</v>
+      </c>
+      <c r="O198" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_1228_연금저축_하이드림연금보험.xlsx
+++ b/output/upload/S00027_1228_연금저축_하이드림연금보험.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW216"/>
+  <dimension ref="A1:AW251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -17169,6 +17169,2386 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>999</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>5</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>999</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>6</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>999</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>7</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>N8</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
+        <v>999</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>8</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>N9</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>999</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>9</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>999</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>10</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>999</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>15</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
+        <v>999</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>20</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L225" t="n">
+        <v>999</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L226" t="n">
+        <v>999</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>55</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
+        <v>999</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>56</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
+        <v>999</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>57</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L229" t="n">
+        <v>999</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>58</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L230" t="n">
+        <v>999</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>59</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L231" t="n">
+        <v>999</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>60</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L232" t="n">
+        <v>999</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>61</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L233" t="n">
+        <v>999</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>62</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
+        <v>999</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>63</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L235" t="n">
+        <v>999</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>64</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
+        <v>999</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>65</v>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L237" t="n">
+        <v>999</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>66</v>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
+        <v>999</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N238" t="n">
+        <v>67</v>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L239" t="n">
+        <v>999</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N239" t="n">
+        <v>68</v>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L240" t="n">
+        <v>999</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N240" t="n">
+        <v>69</v>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L241" t="n">
+        <v>999</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N241" t="n">
+        <v>70</v>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L242" t="n">
+        <v>999</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N242" t="n">
+        <v>71</v>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L243" t="n">
+        <v>999</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>72</v>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L244" t="n">
+        <v>999</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>73</v>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L245" t="n">
+        <v>999</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>74</v>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L246" t="n">
+        <v>999</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>75</v>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L247" t="n">
+        <v>999</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>76</v>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L248" t="n">
+        <v>999</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>77</v>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L249" t="n">
+        <v>999</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N249" t="n">
+        <v>78</v>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L250" t="n">
+        <v>999</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N250" t="n">
+        <v>79</v>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>1228133</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L251" t="n">
+        <v>999</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>80</v>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="I3:N3"/>

--- a/output/upload/S00027_1228_연금저축_하이드림연금보험.xlsx
+++ b/output/upload/S00027_1228_연금저축_하이드림연금보험.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW41"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X59</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -2666,11 +2666,11 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N7" s="6" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>N6</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -2769,11 +2769,11 @@
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N8" s="6" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>X69</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -2872,11 +2872,11 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>N8</t>
+          <t>X78</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -2975,11 +2975,11 @@
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>N9</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X55</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -3181,11 +3181,11 @@
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X64</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -3387,11 +3387,11 @@
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>X73</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3489,11 +3489,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X55</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X56</t>
+          <t>X66</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X57</t>
+          <t>X75</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X58</t>
+          <t>X71</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X59</t>
+          <t>X61</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3897,11 +3897,11 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X61</t>
+          <t>X76</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X62</t>
+          <t>X79</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X63</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -4101,11 +4101,11 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X64</t>
+          <t>X62</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>X57</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X66</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X67</t>
+          <t>X58</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X68</t>
+          <t>X67</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X69</t>
+          <t>X68</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X74</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X71</t>
+          <t>X56</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X73</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4781,11 +4781,11 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X74</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4849,11 +4849,11 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X75</t>
+          <t>X63</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X76</t>
+          <t>X77</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4989,281 +4989,9 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O37" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1228133</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1228133</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>X77</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>999</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>77</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1228133</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1228133</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>X78</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>999</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>78</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1228133</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1228133</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>X79</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>999</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>79</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1228133</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1228133</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>한화생명 연금저축 하이드림연금보험(1종 신계약체결용)종신연금형</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>X80</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>999</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>80</v>
-      </c>
-      <c r="O41" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
